--- a/docs/SSPU_Academic_Programs_Template.xlsx
+++ b/docs/SSPU_Academic_Programs_Template.xlsx
@@ -1,41 +1,306 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Exam Smart Dashboard\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE3DAEA-37A3-4325-9E83-0B4553BB9F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Program_Mapping_Registry" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Program_Mapping_Registry!$A$1:$F$32</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="86">
+  <si>
+    <t>Sr. No.</t>
+  </si>
+  <si>
+    <t>Program Code</t>
+  </si>
+  <si>
+    <t>Program Name</t>
+  </si>
+  <si>
+    <t>School Name</t>
+  </si>
+  <si>
+    <t>Primary Coordinator Email/Name</t>
+  </si>
+  <si>
+    <t>Alternate Coordinator Email/Name</t>
+  </si>
+  <si>
+    <t>School of Construction Engineering and Infrastructure Management</t>
+  </si>
+  <si>
+    <t>Mr. Prathmesh Londhe (prathmesh.londhe@sspu.ac.in)</t>
+  </si>
+  <si>
+    <t>Mr. Rajkumar Wankhade (Rajkumar.wankhade@sspu.ac.in)</t>
+  </si>
+  <si>
+    <t>School of Mechatronics Engineering</t>
+  </si>
+  <si>
+    <t>Mr. Amit Vartikar (Amit.Vartikar@sspu.ac.in)</t>
+  </si>
+  <si>
+    <t>Ms. Shreyasi Joshi (shreyasi.joshi@sspu.ac.in)</t>
+  </si>
+  <si>
+    <t>B.Arch.</t>
+  </si>
+  <si>
+    <t>B. Arch</t>
+  </si>
+  <si>
+    <t>B.Des.ID</t>
+  </si>
+  <si>
+    <t>B. Des. (Interior Design)</t>
+  </si>
+  <si>
+    <t>B.Sc. B&amp;W</t>
+  </si>
+  <si>
+    <t>B.Sc. (Beauty &amp; Wellness)</t>
+  </si>
+  <si>
+    <t>B.Sc. DS</t>
+  </si>
+  <si>
+    <t>B.Sc. (Data Science)</t>
+  </si>
+  <si>
+    <t>B.sc. NSD</t>
+  </si>
+  <si>
+    <t>B.Sc. (Nutritional Sciences and Dietetics)</t>
+  </si>
+  <si>
+    <t>B.Tech CEM</t>
+  </si>
+  <si>
+    <t>B.Tech (Construction Engineering and Management)</t>
+  </si>
+  <si>
+    <t>B.Tech CEM(WILP)</t>
+  </si>
+  <si>
+    <t>B.Tech. Construction Engineering and Management (WILP)</t>
+  </si>
+  <si>
+    <t>B.Tech CS&amp;IT</t>
+  </si>
+  <si>
+    <t>B.Tech [Computer Science &amp; IT (Cyber Security)]</t>
+  </si>
+  <si>
+    <t>B.Tech S&amp;SE</t>
+  </si>
+  <si>
+    <t>B.Tech (Smart and Sustainable Energy)</t>
+  </si>
+  <si>
+    <t>B.Tech. AI&amp;ML</t>
+  </si>
+  <si>
+    <t>B.Tech (Artificial Intelligence and Machine learning)</t>
+  </si>
+  <si>
+    <t>B.Tech. Auto Eng</t>
+  </si>
+  <si>
+    <t>B.Tech (Automobile Engineering)</t>
+  </si>
+  <si>
+    <t>B.Tech. Mech Eng</t>
+  </si>
+  <si>
+    <t>B.Tech (Mechatronics Engineering)</t>
+  </si>
+  <si>
+    <t>B.Tech-Defence</t>
+  </si>
+  <si>
+    <t>B.Tech (Defence Technology)</t>
+  </si>
+  <si>
+    <t>BBA.Fintech</t>
+  </si>
+  <si>
+    <t>BBA (Fintech)</t>
+  </si>
+  <si>
+    <t>BBA-DMM</t>
+  </si>
+  <si>
+    <t>BBA (Digital Media Marketing)</t>
+  </si>
+  <si>
+    <t>BBA-L&amp;SCM</t>
+  </si>
+  <si>
+    <t>BBA (Logistics and Supply Chain Management)</t>
+  </si>
+  <si>
+    <t>BBA-P&amp;TM</t>
+  </si>
+  <si>
+    <t>BBA (Ports &amp; Terminal Management)</t>
+  </si>
+  <si>
+    <t>BBA-R&amp;E-COM</t>
+  </si>
+  <si>
+    <t>BBA (Retail &amp; E-Commerce Management)</t>
+  </si>
+  <si>
+    <t>DIP(AME)</t>
+  </si>
+  <si>
+    <t>Diploma in Advanced Manufacturing Excellence</t>
+  </si>
+  <si>
+    <t>DIP(MA)</t>
+  </si>
+  <si>
+    <t>Diploma in Manufacturing Automation</t>
+  </si>
+  <si>
+    <t>DIP(ME)</t>
+  </si>
+  <si>
+    <t>Diploma in Manufacturing Excellence</t>
+  </si>
+  <si>
+    <t>M.Plan.</t>
+  </si>
+  <si>
+    <t>M. Plan. (Urban Planning)</t>
+  </si>
+  <si>
+    <t>M.Sc. DS</t>
+  </si>
+  <si>
+    <t>M.Sc. (Data Science)</t>
+  </si>
+  <si>
+    <t>M.Sc. NSD</t>
+  </si>
+  <si>
+    <t>M.Sc. (Nutritional Sciences and Ditetics)</t>
+  </si>
+  <si>
+    <t>M.Tech. Mech Eng (IOT,AI&amp;ROB)</t>
+  </si>
+  <si>
+    <t>M.Tech [Mechatronics Engineering (IOT, AI &amp; Robotics)]</t>
+  </si>
+  <si>
+    <t>MBA(L&amp;SCM)</t>
+  </si>
+  <si>
+    <t>MBA (Logistics and Supply Chain Management)</t>
+  </si>
+  <si>
+    <t>B.Tech. MSM(WILP)</t>
+  </si>
+  <si>
+    <t>B.Tech. Mechanical and Smart Manufacturing (WILP)</t>
+  </si>
+  <si>
+    <t>MBA(FinTech)</t>
+  </si>
+  <si>
+    <t>MBA (FinTech)</t>
+  </si>
+  <si>
+    <t>MBA (Digital Marketing)</t>
+  </si>
+  <si>
+    <t>B.Tech Semicondu Eng</t>
+  </si>
+  <si>
+    <t>B.Tech (Semiconductor Engineering)</t>
+  </si>
+  <si>
+    <t>BTechAuto(WILP)</t>
+  </si>
+  <si>
+    <t>B. Tech. Automobile Engineering (WILP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School of Architecture, Urban Development &amp; Planning </t>
+  </si>
+  <si>
+    <t>School of Beauty and Wellness</t>
+  </si>
+  <si>
+    <t>School of Data Science</t>
+  </si>
+  <si>
+    <t>School of Nutrition and Dietetics</t>
+  </si>
+  <si>
+    <t>School of Computer Science &amp; Information Technology</t>
+  </si>
+  <si>
+    <t>School of Sustainability Studies</t>
+  </si>
+  <si>
+    <t>School of Automobile Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">School of Defence Technology </t>
+  </si>
+  <si>
+    <t>School of Banking, Financial Services, and Insurance</t>
+  </si>
+  <si>
+    <t>School of Media Management</t>
+  </si>
+  <si>
+    <t>School of Ports, Terminal Management and Logistics</t>
+  </si>
+  <si>
+    <t>School of Retail Management</t>
+  </si>
+  <si>
+    <t>School of Semiconductor Engineering</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -43,16 +308,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -60,18 +337,74 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,192 +729,693 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="50.4140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Sr. No.</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Program Code</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Program Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>School Name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Primary Coordinator Email/Name</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Alternate Coordinator Email/Name</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>BTECH-CEM</v>
-      </c>
-      <c r="C2" t="str">
-        <v>B.Tech. Construction Engineering &amp; Management</v>
-      </c>
-      <c r="D2" t="str">
-        <v>School of Construction Engineering and Infrastructure Management</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Mr. Prathmesh Londhe (prathmesh.londhe@sspu.ac.in)</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Mr. Rajkumar Wankhade (Rajkumar.wankhade@sspu.ac.in)</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>BTECH-MECH</v>
-      </c>
-      <c r="C3" t="str">
-        <v>B.Tech. Mechatronics Engineering</v>
-      </c>
-      <c r="D3" t="str">
-        <v>School of Mechatronics Engineering</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Mr. Amit Vartikar (Amit.Vartikar@sspu.ac.in)</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Mr. Prathmesh Londhe (prathmesh.londhe@sspu.ac.in)</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>BTECH-CSAI</v>
-      </c>
-      <c r="C4" t="str">
-        <v>B.Tech. Computer Science &amp; AI</v>
-      </c>
-      <c r="D4" t="str">
-        <v>School of Computer Science &amp; Artificial Intelligence</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Mr. Rajkumar Wankhade (Rajkumar.wankhade@sspu.ac.in)</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Mr. Amit Vartikar (Amit.Vartikar@sspu.ac.in)</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>BTECH-EEE</v>
-      </c>
-      <c r="C5" t="str">
-        <v>B.Tech. Electrical &amp; Electronics</v>
-      </c>
-      <c r="D5" t="str">
-        <v>School of Electrical &amp; Electronics Engineering</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Ms. Shreyasi Joshi (shreyasi.joshi@sspu.ac.in)</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Mr. Prathmesh Londhe (prathmesh.londhe@sspu.ac.in)</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>BARCH</v>
-      </c>
-      <c r="C6" t="str">
-        <v>B.Arch. Architecture &amp; Urban Design</v>
-      </c>
-      <c r="D6" t="str">
-        <v>School of Architecture, Urban Development &amp; Planning</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Mr. Amit Vartikar (Amit.Vartikar@sspu.ac.in)</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Ms. Shreyasi Joshi (shreyasi.joshi@sspu.ac.in)</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>BBA-LSCM</v>
-      </c>
-      <c r="C7" t="str">
-        <v>BBA Logistics &amp; Supply Chain Management</v>
-      </c>
-      <c r="D7" t="str">
-        <v>School of Management &amp; Commerce</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Mr. Prathmesh Londhe (prathmesh.londhe@sspu.ac.in)</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Mr. Rajkumar Wankhade (Rajkumar.wankhade@sspu.ac.in)</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="B7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>BBA-RET</v>
-      </c>
-      <c r="C8" t="str">
-        <v>BBA Retail &amp; E-Commerce Management</v>
-      </c>
-      <c r="D8" t="str">
-        <v>School of Management &amp; Commerce</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Mr. Rajkumar Wankhade (Rajkumar.wankhade@sspu.ac.in)</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Ms. Shreyasi Joshi (shreyasi.joshi@sspu.ac.in)</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="B8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>BSC-DS</v>
-      </c>
-      <c r="C9" t="str">
-        <v>B.Sc. Data Science &amp; Artificial Intelligence</v>
-      </c>
-      <c r="D9" t="str">
-        <v>School of Computer Science &amp; Artificial Intelligence</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Ms. Shreyasi Joshi (shreyasi.joshi@sspu.ac.in)</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Mr. Amit Vartikar (Amit.Vartikar@sspu.ac.in)</v>
-      </c>
-    </row>
+      <c r="B9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="34" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="35" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="36" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="37" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="38" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="39" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="40" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="41" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="42" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="43" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="44" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="45" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="46" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="47" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="48" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="49" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="50" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="51" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="52" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="53" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="54" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="55" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="56" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="57" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="58" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="61" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <autoFilter ref="A1:F32" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F32">
+      <sortCondition ref="E1:E32"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>